--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -4,25 +4,37 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Summary Metrics" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Execution Summary" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Total Defined</t>
-  </si>
-  <si>
-    <t>Total Automated</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Metric Category</t>
+  </si>
+  <si>
+    <t>Value / Count</t>
+  </si>
+  <si>
+    <t>Total Defined Specs</t>
+  </si>
+  <si>
+    <t>Appium Automated</t>
+  </si>
+  <si>
+    <t>Selenium Automated</t>
+  </si>
+  <si>
+    <t>API Automated</t>
+  </si>
+  <si>
+    <t>k6 Automated</t>
+  </si>
+  <si>
+    <t>Security Automated</t>
   </si>
   <si>
     <t>Total Executed</t>
@@ -43,10 +55,16 @@
     <t>Not Applicable</t>
   </si>
   <si>
-    <t>Pass Percentage (%)</t>
-  </si>
-  <si>
-    <t>100%</t>
+    <t>Executed-Test Pass Percentage</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>Full-Suite Completion Percentage</t>
+  </si>
+  <si>
+    <t>4.59%</t>
   </si>
 </sst>
 </file>
@@ -75,7 +93,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="595959"/>
+        <fgColor rgb="1F497D"/>
       </patternFill>
     </fill>
   </fills>
@@ -433,11 +451,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -453,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>510</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -485,7 +503,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -493,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,15 +527,55 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -64,7 +64,7 @@
     <t>Full-Suite Completion Percentage</t>
   </si>
   <si>
-    <t>4.59%</t>
+    <t>60.92%</t>
   </si>
 </sst>
 </file>
@@ -471,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>545</v>
+        <v>870</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -503,7 +503,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">

--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Metric Category</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>Full-Suite Completion Percentage</t>
-  </si>
-  <si>
-    <t>60.92%</t>
   </si>
 </sst>
 </file>
@@ -519,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>530</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>530</v>
+        <v>870</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -575,7 +572,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
